--- a/Lista_Invitados_Boda(1).xlsx
+++ b/Lista_Invitados_Boda(1).xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="149">
   <si>
     <t>No.</t>
   </si>
@@ -451,6 +451,24 @@
   </si>
   <si>
     <t>OSMAN ROSTRAN</t>
+  </si>
+  <si>
+    <t>ERICK GUSTAVO VALLADARES FIALLOS Y ESPOSA</t>
+  </si>
+  <si>
+    <t>PAUL TURCIOS Y ESPOSA</t>
+  </si>
+  <si>
+    <t>LEONARDO FLORES Y ESPOSA</t>
+  </si>
+  <si>
+    <t>SUYAPA MOLINA</t>
+  </si>
+  <si>
+    <t>MANUEL LOPEZ Y FAMILIA</t>
+  </si>
+  <si>
+    <t>LUIS ALONSO DIAZ IGLESIAS Y ESPOSA</t>
   </si>
 </sst>
 </file>
@@ -793,7 +811,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C142"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
@@ -2362,6 +2380,72 @@
         <v>2</v>
       </c>
     </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>143</v>
+      </c>
+      <c r="C143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>144</v>
+      </c>
+      <c r="C144">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>145</v>
+      </c>
+      <c r="C145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>146</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>147</v>
+      </c>
+      <c r="C147">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>148</v>
+      </c>
+      <c r="C148">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Lista_Invitados_Boda(1).xlsx
+++ b/Lista_Invitados_Boda(1).xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="158">
   <si>
     <t>No.</t>
   </si>
@@ -469,6 +469,33 @@
   </si>
   <si>
     <t>LUIS ALONSO DIAZ IGLESIAS Y ESPOSA</t>
+  </si>
+  <si>
+    <t>CORONADO ALVARADO Y ESPOSA</t>
+  </si>
+  <si>
+    <t>NELDA RIVAS</t>
+  </si>
+  <si>
+    <t>ARMANDO RIVAS Y ESPOSA</t>
+  </si>
+  <si>
+    <t>ARTURO RODRIGUEZ Y ESPOSA</t>
+  </si>
+  <si>
+    <t>JOEL GODOY</t>
+  </si>
+  <si>
+    <t>JUAN PINEDA Y ESPOSA</t>
+  </si>
+  <si>
+    <t>HECTOR GÓMEZ Y ESPOSA</t>
+  </si>
+  <si>
+    <t>MANUEL ALMENDADES Y ESPOSA</t>
+  </si>
+  <si>
+    <t>MIGUEL CASTELLANOS Y ESPOSA</t>
   </si>
 </sst>
 </file>
@@ -811,7 +838,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C157"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
@@ -2446,6 +2473,105 @@
         <v>2</v>
       </c>
     </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>149</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>150</v>
+      </c>
+      <c r="C150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>151</v>
+      </c>
+      <c r="C151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>152</v>
+      </c>
+      <c r="C152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>153</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>154</v>
+      </c>
+      <c r="C154">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>155</v>
+      </c>
+      <c r="C155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>156</v>
+      </c>
+      <c r="C156">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>157</v>
+      </c>
+      <c r="C157">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Lista_Invitados_Boda(1).xlsx
+++ b/Lista_Invitados_Boda(1).xlsx
@@ -2481,7 +2481,7 @@
         <v>149</v>
       </c>
       <c r="C149">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">

--- a/Lista_Invitados_Boda(1).xlsx
+++ b/Lista_Invitados_Boda(1).xlsx
@@ -492,10 +492,10 @@
     <t>HECTOR GÓMEZ Y ESPOSA</t>
   </si>
   <si>
-    <t>MANUEL ALMENDADES Y ESPOSA</t>
-  </si>
-  <si>
     <t>MIGUEL CASTELLANOS Y ESPOSA</t>
+  </si>
+  <si>
+    <t>MANUEL ALMENDARES Y ESPOSA</t>
   </si>
 </sst>
 </file>
@@ -2555,7 +2555,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C156">
         <v>2</v>
@@ -2566,7 +2566,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C157">
         <v>2</v>

--- a/Lista_Invitados_Boda(1).xlsx
+++ b/Lista_Invitados_Boda(1).xlsx
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Invitados!$A$1:$C$140</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" calcOnSave="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="159">
   <si>
     <t>No.</t>
   </si>
@@ -496,6 +496,9 @@
   </si>
   <si>
     <t>MANUEL ALMENDARES Y ESPOSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DORIS SUYAPA BRAN Y HIJO </t>
   </si>
 </sst>
 </file>
@@ -838,7 +841,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C157"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
@@ -2572,6 +2575,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>158</v>
+      </c>
+      <c r="C158">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Lista_Invitados_Boda(1).xlsx
+++ b/Lista_Invitados_Boda(1).xlsx
@@ -15,14 +15,14 @@
     <sheet name="Invitados" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Invitados!$A$1:$C$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Invitados!$A$1:$C$160</definedName>
   </definedNames>
   <calcPr calcId="0" calcOnSave="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="163">
   <si>
     <t>No.</t>
   </si>
@@ -396,18 +396,12 @@
     <t>NESTOR RIVAS</t>
   </si>
   <si>
-    <t>JOSE LUIS ESPINOZA Y ESPOSA</t>
-  </si>
-  <si>
     <t>MARIA Y JESUS</t>
   </si>
   <si>
     <t>PADRE JOSÉ LUIS MERCADO ESCOBAR</t>
   </si>
   <si>
-    <t>NERY LUQUE Y ESPOSA</t>
-  </si>
-  <si>
     <t>SAUL MENDOZA</t>
   </si>
   <si>
@@ -426,15 +420,9 @@
     <t>MIGUEL ANGEL CHAVARRIA Y ESPOSA</t>
   </si>
   <si>
-    <t>GERSON RODRIGUEZ Y ESPOSA</t>
-  </si>
-  <si>
     <t>CRISTIAN ELVIR Y ESPOSA</t>
   </si>
   <si>
-    <t>JUAN VALLECILLO Y ESPOSA</t>
-  </si>
-  <si>
     <t>MAURO ERNESTO VALLADARES Y ESPOSA</t>
   </si>
   <si>
@@ -450,9 +438,6 @@
     <t>NICOLL PORTILLO</t>
   </si>
   <si>
-    <t>OSMAN ROSTRAN</t>
-  </si>
-  <si>
     <t>ERICK GUSTAVO VALLADARES FIALLOS Y ESPOSA</t>
   </si>
   <si>
@@ -499,6 +484,33 @@
   </si>
   <si>
     <t xml:space="preserve">DORIS SUYAPA BRAN Y HIJO </t>
+  </si>
+  <si>
+    <t>JUAN VALLECILLO Y FAMILIA</t>
+  </si>
+  <si>
+    <t>JOSE LUIS MIRANDA Y ESPOSA</t>
+  </si>
+  <si>
+    <t>GERARDO RODRIGUEZ Y ESPOSA</t>
+  </si>
+  <si>
+    <t>ANGEL GONZALEZ Y ESPOSA</t>
+  </si>
+  <si>
+    <t>ANDY ZERON Y FAMILIA</t>
+  </si>
+  <si>
+    <t>OSMAN ROSTRAN Y ESPOSA</t>
+  </si>
+  <si>
+    <t>NERY FELIPE SEGURA Y ESPOSA</t>
+  </si>
+  <si>
+    <t>MERLIN VIDEA Y ESPOSA</t>
+  </si>
+  <si>
+    <t>MERLIN MARADIAGA</t>
   </si>
 </sst>
 </file>
@@ -841,7 +853,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C158"/>
+  <dimension ref="A1:C162"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
@@ -864,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -930,7 +942,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1337,7 +1349,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -1469,10 +1481,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -1744,7 +1756,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C82">
         <v>2</v>
@@ -1898,7 +1910,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C96">
         <v>2</v>
@@ -2242,7 +2254,7 @@
         <v>120</v>
       </c>
       <c r="C127">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -2250,7 +2262,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -2272,7 +2284,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C130">
         <v>3</v>
@@ -2283,10 +2295,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -2297,7 +2309,7 @@
         <v>122</v>
       </c>
       <c r="C132">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -2305,7 +2317,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C133">
         <v>2</v>
@@ -2316,7 +2328,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C134">
         <v>2</v>
@@ -2327,7 +2339,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C135">
         <v>2</v>
@@ -2338,7 +2350,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C136">
         <v>2</v>
@@ -2349,7 +2361,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -2360,7 +2372,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -2371,7 +2383,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C139">
         <v>3</v>
@@ -2382,7 +2394,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="C140">
         <v>2</v>
@@ -2393,7 +2405,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -2404,7 +2416,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="C142">
         <v>2</v>
@@ -2415,7 +2427,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C143">
         <v>2</v>
@@ -2426,7 +2438,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C144">
         <v>2</v>
@@ -2437,7 +2449,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C145">
         <v>2</v>
@@ -2448,7 +2460,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -2459,7 +2471,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C147">
         <v>3</v>
@@ -2470,7 +2482,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C148">
         <v>2</v>
@@ -2481,7 +2493,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C149">
         <v>2</v>
@@ -2492,7 +2504,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C150">
         <v>2</v>
@@ -2503,7 +2515,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C151">
         <v>2</v>
@@ -2514,7 +2526,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C152">
         <v>2</v>
@@ -2525,7 +2537,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -2536,7 +2548,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C154">
         <v>2</v>
@@ -2547,7 +2559,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C155">
         <v>2</v>
@@ -2558,7 +2570,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C156">
         <v>2</v>
@@ -2569,7 +2581,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C157">
         <v>2</v>
@@ -2580,14 +2592,58 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
+        <v>153</v>
+      </c>
+      <c r="C158">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159">
         <v>158</v>
       </c>
-      <c r="C158">
-        <v>2</v>
+      <c r="B159" t="s">
+        <v>157</v>
+      </c>
+      <c r="C159">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>158</v>
+      </c>
+      <c r="C160">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>161</v>
+      </c>
+      <c r="C161">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>162</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C140"/>
+  <autoFilter ref="A1:C160"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Lista_Invitados_Boda(1).xlsx
+++ b/Lista_Invitados_Boda(1).xlsx
@@ -15,14 +15,14 @@
     <sheet name="Invitados" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Invitados!$A$1:$C$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Invitados!$A$1:$C$165</definedName>
   </definedNames>
   <calcPr calcId="0" calcOnSave="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="166">
   <si>
     <t>No.</t>
   </si>
@@ -384,9 +384,6 @@
     <t>ISABEL RIVAS</t>
   </si>
   <si>
-    <t>ARNULFO VALLADARES Y FAMILIA</t>
-  </si>
-  <si>
     <t>MIRIAN GODOY</t>
   </si>
   <si>
@@ -511,6 +508,18 @@
   </si>
   <si>
     <t>MERLIN MARADIAGA</t>
+  </si>
+  <si>
+    <t>NERY LUQUE Y ESPOSA</t>
+  </si>
+  <si>
+    <t>ANTONIO AMAYA Y PADRE AMAYA</t>
+  </si>
+  <si>
+    <t>DOMINGO MONTOYA Y ESPOSA</t>
+  </si>
+  <si>
+    <t>ARNULFO VALLADARES Y ESPOSA</t>
   </si>
 </sst>
 </file>
@@ -853,7 +862,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C162"/>
+  <dimension ref="A1:C165"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
@@ -876,7 +885,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -942,7 +951,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1349,7 +1358,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -1481,7 +1490,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57">
         <v>3</v>
@@ -1756,7 +1765,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C82">
         <v>2</v>
@@ -1910,7 +1919,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C96">
         <v>2</v>
@@ -2229,7 +2238,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -2251,7 +2260,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -2262,7 +2271,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -2273,7 +2282,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -2284,7 +2293,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C130">
         <v>3</v>
@@ -2295,7 +2304,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -2306,7 +2315,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -2317,7 +2326,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C133">
         <v>2</v>
@@ -2328,7 +2337,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C134">
         <v>2</v>
@@ -2339,7 +2348,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C135">
         <v>2</v>
@@ -2350,7 +2359,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C136">
         <v>2</v>
@@ -2361,7 +2370,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -2372,7 +2381,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -2383,7 +2392,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C139">
         <v>3</v>
@@ -2394,7 +2403,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C140">
         <v>2</v>
@@ -2405,7 +2414,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -2416,7 +2425,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C142">
         <v>2</v>
@@ -2427,7 +2436,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C143">
         <v>2</v>
@@ -2438,7 +2447,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C144">
         <v>2</v>
@@ -2449,7 +2458,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C145">
         <v>2</v>
@@ -2460,7 +2469,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -2471,7 +2480,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C147">
         <v>3</v>
@@ -2482,7 +2491,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C148">
         <v>2</v>
@@ -2493,7 +2502,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C149">
         <v>2</v>
@@ -2504,7 +2513,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C150">
         <v>2</v>
@@ -2515,7 +2524,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C151">
         <v>2</v>
@@ -2526,7 +2535,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C152">
         <v>2</v>
@@ -2537,7 +2546,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -2548,7 +2557,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C154">
         <v>2</v>
@@ -2559,7 +2568,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C155">
         <v>2</v>
@@ -2570,7 +2579,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C156">
         <v>2</v>
@@ -2581,7 +2590,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C157">
         <v>2</v>
@@ -2592,7 +2601,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C158">
         <v>2</v>
@@ -2603,7 +2612,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C159">
         <v>2</v>
@@ -2614,7 +2623,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C160">
         <v>3</v>
@@ -2625,7 +2634,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C161">
         <v>2</v>
@@ -2636,14 +2645,47 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
+        <v>161</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163">
         <v>162</v>
       </c>
-      <c r="C162">
-        <v>1</v>
+      <c r="B163" t="s">
+        <v>162</v>
+      </c>
+      <c r="C163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>163</v>
+      </c>
+      <c r="C164">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>164</v>
+      </c>
+      <c r="C165">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C160"/>
+  <autoFilter ref="A1:C165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Lista_Invitados_Boda(1).xlsx
+++ b/Lista_Invitados_Boda(1).xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="169">
   <si>
     <t>No.</t>
   </si>
@@ -520,6 +520,15 @@
   </si>
   <si>
     <t>ARNULFO VALLADARES Y ESPOSA</t>
+  </si>
+  <si>
+    <t>RONY MONCADA Y ESPOSA</t>
+  </si>
+  <si>
+    <t>WALTER ALBERTO MONTERROSO Y FAMILIA</t>
+  </si>
+  <si>
+    <t>LORENZO ANTONIO ZERON Y FAMILIA</t>
   </si>
 </sst>
 </file>
@@ -862,7 +871,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C165"/>
+  <dimension ref="A1:C168"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
@@ -2684,6 +2693,39 @@
         <v>2</v>
       </c>
     </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>166</v>
+      </c>
+      <c r="C166">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>167</v>
+      </c>
+      <c r="C167">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>168</v>
+      </c>
+      <c r="C168">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
